--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,6 +1143,551 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131912056</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57901</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720608</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6368395</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök vid foten av död gran. Talrika insektshål.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131912097</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106166</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720408</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6368255</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131912058</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57901</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720398</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6368271</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök vid foten av död gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131912092</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100095</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720388</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6368351</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131912057</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57901</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720423</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6368432</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1149,7 +1149,7 @@
         <v>131912056</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>131912097</v>
       </c>
       <c r="B7" t="n">
-        <v>106166</v>
+        <v>106170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>131912058</v>
       </c>
       <c r="B8" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,48 +1472,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912092</v>
+        <v>131912057</v>
       </c>
       <c r="B9" t="n">
-        <v>100095</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720388</v>
+        <v>720423</v>
       </c>
       <c r="R9" t="n">
-        <v>6368351</v>
+        <v>6368432</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1552,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,53 +1584,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912057</v>
+        <v>131912092</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>100098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720423</v>
+        <v>720388</v>
       </c>
       <c r="R10" t="n">
-        <v>6368432</v>
+        <v>6368351</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1149,7 +1149,7 @@
         <v>131912056</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>131912097</v>
       </c>
       <c r="B7" t="n">
-        <v>106170</v>
+        <v>106175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>131912058</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,53 +1472,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912057</v>
+        <v>131912092</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>100103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720423</v>
+        <v>720388</v>
       </c>
       <c r="R9" t="n">
-        <v>6368432</v>
+        <v>6368351</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1547,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1561,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1584,48 +1579,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912092</v>
+        <v>131912057</v>
       </c>
       <c r="B10" t="n">
-        <v>100098</v>
+        <v>57909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720388</v>
+        <v>720423</v>
       </c>
       <c r="R10" t="n">
-        <v>6368351</v>
+        <v>6368432</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1261,7 +1261,7 @@
         <v>131912097</v>
       </c>
       <c r="B7" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131912092</v>
       </c>
       <c r="B10" t="n">
-        <v>100147</v>
+        <v>100150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1472,53 +1472,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912057</v>
+        <v>131912092</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>100150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720423</v>
+        <v>720388</v>
       </c>
       <c r="R9" t="n">
-        <v>6368432</v>
+        <v>6368351</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1547,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1561,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1584,48 +1579,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912092</v>
+        <v>131912057</v>
       </c>
       <c r="B10" t="n">
-        <v>100150</v>
+        <v>57945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720388</v>
+        <v>720423</v>
       </c>
       <c r="R10" t="n">
-        <v>6368351</v>
+        <v>6368432</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1472,48 +1472,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912092</v>
+        <v>131912057</v>
       </c>
       <c r="B9" t="n">
-        <v>100150</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720388</v>
+        <v>720423</v>
       </c>
       <c r="R9" t="n">
-        <v>6368351</v>
+        <v>6368432</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1552,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,53 +1584,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912057</v>
+        <v>131912092</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>100150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720423</v>
+        <v>720388</v>
       </c>
       <c r="R10" t="n">
-        <v>6368432</v>
+        <v>6368351</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1149,7 +1149,7 @@
         <v>131912056</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>131912097</v>
       </c>
       <c r="B7" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>131912058</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>131912092</v>
       </c>
       <c r="B9" t="n">
-        <v>100150</v>
+        <v>100158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131912057</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1149,7 +1149,7 @@
         <v>131912056</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>131912097</v>
       </c>
       <c r="B7" t="n">
-        <v>106230</v>
+        <v>106241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>131912058</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,48 +1472,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912092</v>
+        <v>131912057</v>
       </c>
       <c r="B9" t="n">
-        <v>100158</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720388</v>
+        <v>720423</v>
       </c>
       <c r="R9" t="n">
-        <v>6368351</v>
+        <v>6368432</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1552,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,53 +1584,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912057</v>
+        <v>131912092</v>
       </c>
       <c r="B10" t="n">
-        <v>57946</v>
+        <v>100168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720423</v>
+        <v>720388</v>
       </c>
       <c r="R10" t="n">
-        <v>6368432</v>
+        <v>6368351</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,6 +1689,1168 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132846303</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132846309</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132846307</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106245</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132846312</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132846304</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107518</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132846299</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99782</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132846305</v>
+      </c>
+      <c r="B17" t="n">
+        <v>109838</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1489</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Alvarstånds</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132846296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>107518</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720471</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6368305</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>på fin karstmark</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132846311</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132846310</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99782</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132846297</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720471</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6368305</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på fin karstmark, i fylld karstspricka</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846309</v>
+        <v>132846307</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>106245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846307</v>
+        <v>132846309</v>
       </c>
       <c r="B13" t="n">
-        <v>106245</v>
+        <v>5495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2305,44 +2305,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B17" t="n">
-        <v>109838</v>
+        <v>107518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2352,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R17" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2392,7 +2384,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,36 +2412,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B18" t="n">
-        <v>107518</v>
+        <v>109838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R18" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1694,7 +1694,7 @@
         <v>132846303</v>
       </c>
       <c r="B11" t="n">
-        <v>99148</v>
+        <v>99150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846307</v>
+        <v>132846309</v>
       </c>
       <c r="B12" t="n">
-        <v>106245</v>
+        <v>5495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846309</v>
+        <v>132846307</v>
       </c>
       <c r="B13" t="n">
-        <v>5495</v>
+        <v>106247</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
         <v>132846312</v>
       </c>
       <c r="B14" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>132846304</v>
       </c>
       <c r="B15" t="n">
-        <v>107518</v>
+        <v>107520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>132846299</v>
       </c>
       <c r="B16" t="n">
-        <v>99782</v>
+        <v>99784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,36 +2305,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B17" t="n">
-        <v>107518</v>
+        <v>109840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2344,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R17" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,44 +2420,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B18" t="n">
-        <v>109838</v>
+        <v>107520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R18" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,7 +2530,7 @@
         <v>132846311</v>
       </c>
       <c r="B19" t="n">
-        <v>99148</v>
+        <v>99150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>132846310</v>
       </c>
       <c r="B20" t="n">
-        <v>99782</v>
+        <v>99784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>132846297</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1694,7 +1694,7 @@
         <v>132846303</v>
       </c>
       <c r="B11" t="n">
-        <v>99150</v>
+        <v>99151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>132846307</v>
       </c>
       <c r="B13" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>132846312</v>
       </c>
       <c r="B14" t="n">
-        <v>99156</v>
+        <v>99157</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>132846304</v>
       </c>
       <c r="B15" t="n">
-        <v>107520</v>
+        <v>107521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>132846299</v>
       </c>
       <c r="B16" t="n">
-        <v>99784</v>
+        <v>99785</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,44 +2305,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B17" t="n">
-        <v>109840</v>
+        <v>107521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2352,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R17" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2392,7 +2384,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,36 +2412,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B18" t="n">
-        <v>107520</v>
+        <v>109841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R18" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,7 +2530,7 @@
         <v>132846311</v>
       </c>
       <c r="B19" t="n">
-        <v>99150</v>
+        <v>99151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>132846310</v>
       </c>
       <c r="B20" t="n">
-        <v>99784</v>
+        <v>99785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>132846297</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -2305,44 +2305,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B17" t="n">
-        <v>109852</v>
+        <v>107532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2352,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R17" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2392,7 +2384,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,36 +2412,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B18" t="n">
-        <v>107532</v>
+        <v>109852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R18" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846309</v>
+        <v>132846307</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>106258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846307</v>
+        <v>132846309</v>
       </c>
       <c r="B13" t="n">
-        <v>106258</v>
+        <v>5495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2305,36 +2305,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B17" t="n">
-        <v>107532</v>
+        <v>109852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2344,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R17" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,44 +2420,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B18" t="n">
-        <v>109852</v>
+        <v>107532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R18" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846307</v>
+        <v>132846309</v>
       </c>
       <c r="B12" t="n">
-        <v>106258</v>
+        <v>5495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846309</v>
+        <v>132846307</v>
       </c>
       <c r="B13" t="n">
-        <v>5495</v>
+        <v>106258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2305,36 +2305,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B17" t="n">
-        <v>107532</v>
+        <v>109852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2344,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R17" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,44 +2420,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B18" t="n">
-        <v>109852</v>
+        <v>107532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R18" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -2305,36 +2305,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B17" t="n">
-        <v>107532</v>
+        <v>109852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2344,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R17" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,44 +2420,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B18" t="n">
-        <v>109852</v>
+        <v>107532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R18" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -1694,7 +1694,7 @@
         <v>132846303</v>
       </c>
       <c r="B11" t="n">
-        <v>99159</v>
+        <v>99161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846309</v>
+        <v>132846307</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>106260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846307</v>
+        <v>132846309</v>
       </c>
       <c r="B13" t="n">
-        <v>106258</v>
+        <v>5495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
         <v>132846312</v>
       </c>
       <c r="B14" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>132846304</v>
       </c>
       <c r="B15" t="n">
-        <v>107532</v>
+        <v>107534</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>132846299</v>
       </c>
       <c r="B16" t="n">
-        <v>99793</v>
+        <v>99795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>132846296</v>
       </c>
       <c r="B17" t="n">
-        <v>107532</v>
+        <v>107534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>132846305</v>
       </c>
       <c r="B18" t="n">
-        <v>109852</v>
+        <v>109854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>132846311</v>
       </c>
       <c r="B19" t="n">
-        <v>99159</v>
+        <v>99161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>132846310</v>
       </c>
       <c r="B20" t="n">
-        <v>99793</v>
+        <v>99795</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>132846297</v>
       </c>
       <c r="B21" t="n">
-        <v>91338</v>
+        <v>91340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -2305,36 +2305,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846296</v>
+        <v>132846305</v>
       </c>
       <c r="B17" t="n">
-        <v>107534</v>
+        <v>109854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1489</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2344,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720471</v>
+        <v>720452</v>
       </c>
       <c r="R17" t="n">
-        <v>6368305</v>
+        <v>6368310</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2384,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på fin karstmark</t>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,44 +2420,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846305</v>
+        <v>132846296</v>
       </c>
       <c r="B18" t="n">
-        <v>109854</v>
+        <v>107534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1489</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720452</v>
+        <v>720471</v>
       </c>
       <c r="R18" t="n">
-        <v>6368310</v>
+        <v>6368305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bladrosetter</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105058135</v>
+        <v>105058040</v>
       </c>
       <c r="B2" t="n">
-        <v>102366</v>
+        <v>109837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2078</v>
+        <v>1489</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråfingerört</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Potentilla incana</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gasmyr (N-spets) 850 m ONO, Gtl</t>
+          <t>Gasmyr (N-spets) 950 m ONO, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720441</v>
+        <v>720480</v>
       </c>
       <c r="R2" t="n">
-        <v>6368282</v>
+        <v>6368403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera ruggar.</t>
+          <t>Ardre 4.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst.</t>
+          <t>Kalkglänta, ol båglik,</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,7 +798,7 @@
         <v>105058077</v>
       </c>
       <c r="B3" t="n">
-        <v>109276</v>
+        <v>109837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +918,7 @@
         <v>105058113</v>
       </c>
       <c r="B4" t="n">
-        <v>109276</v>
+        <v>109837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1038,7 @@
         <v>105058136</v>
       </c>
       <c r="B5" t="n">
-        <v>109276</v>
+        <v>109837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,53 +1155,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131912056</v>
+        <v>132846298</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>109918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1489</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720608</v>
+        <v>720466</v>
       </c>
       <c r="R6" t="n">
-        <v>6368395</v>
+        <v>6368312</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,17 +1232,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död gran. Talrika insektshål.</t>
+          <t>Rosett och vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,33 +1251,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131912097</v>
+        <v>132846305</v>
       </c>
       <c r="B7" t="n">
-        <v>106241</v>
+        <v>109918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,34 +1281,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>1489</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720408</v>
+        <v>720452</v>
       </c>
       <c r="R7" t="n">
-        <v>6368255</v>
+        <v>6368310</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1323,12 +1347,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,76 +1366,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131912058</v>
+        <v>105058135</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>102864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2078</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråfingerört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Potentilla incana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Gasmyr (N-spets) 850 m ONO, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720398</v>
+        <v>720441</v>
       </c>
       <c r="R8" t="n">
-        <v>6368271</v>
+        <v>6368282</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,17 +1450,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2000-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2000-08-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död gran.</t>
+          <t>Flera ruggar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1474,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll med karst.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1468,57 +1488,67 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131912057</v>
+        <v>132846297</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>91394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4191</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720423</v>
+        <v>720471</v>
       </c>
       <c r="R9" t="n">
-        <v>6368432</v>
+        <v>6368305</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,17 +1572,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
+          <t>på fin karstmark, i fylld karstspricka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,33 +1591,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131912092</v>
+        <v>131912056</v>
       </c>
       <c r="B10" t="n">
-        <v>100168</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,37 +1621,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720388</v>
+        <v>720608</v>
       </c>
       <c r="R10" t="n">
-        <v>6368351</v>
+        <v>6368395</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1690,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>Födosök vid foten av död gran. Talrika insektshål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1704,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1691,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132846303</v>
+        <v>131912057</v>
       </c>
       <c r="B11" t="n">
-        <v>99161</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,45 +1733,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720452</v>
+        <v>720423</v>
       </c>
       <c r="R11" t="n">
-        <v>6368310</v>
+        <v>6368432</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,12 +1792,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosök vid foten av död tall. Mycket gott om insektshål på trädet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,29 +1811,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132846307</v>
+        <v>131912058</v>
       </c>
       <c r="B12" t="n">
-        <v>106260</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,37 +1845,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720419</v>
+        <v>720398</v>
       </c>
       <c r="R12" t="n">
-        <v>6368251</v>
+        <v>6368271</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,12 +1904,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosök vid foten av död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,16 +1925,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1897,7 +1949,7 @@
         <v>132846309</v>
       </c>
       <c r="B13" t="n">
-        <v>5495</v>
+        <v>5497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132846312</v>
+        <v>132846303</v>
       </c>
       <c r="B14" t="n">
-        <v>99167</v>
+        <v>99224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,32 +2054,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219874</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2038,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720419</v>
+        <v>720452</v>
       </c>
       <c r="R14" t="n">
-        <v>6368251</v>
+        <v>6368310</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2101,27 +2149,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132846304</v>
+        <v>132846311</v>
       </c>
       <c r="B15" t="n">
-        <v>107534</v>
+        <v>99224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2130,8 +2178,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2140,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720452</v>
+        <v>720419</v>
       </c>
       <c r="R15" t="n">
-        <v>6368310</v>
+        <v>6368251</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2203,37 +2259,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132846299</v>
+        <v>132846312</v>
       </c>
       <c r="B16" t="n">
-        <v>99795</v>
+        <v>99230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222309</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2242,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720452</v>
+        <v>720419</v>
       </c>
       <c r="R16" t="n">
-        <v>6368310</v>
+        <v>6368251</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2305,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132846305</v>
+        <v>131912097</v>
       </c>
       <c r="B17" t="n">
-        <v>109854</v>
+        <v>106324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,46 +2380,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1489</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720452</v>
+        <v>720408</v>
       </c>
       <c r="R17" t="n">
-        <v>6368310</v>
+        <v>6368255</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2382,17 +2434,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bladrosetter</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,68 +2448,68 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846296</v>
+        <v>132846307</v>
       </c>
       <c r="B18" t="n">
-        <v>107534</v>
+        <v>106324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ardre, Botvalde 1:33 1, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720471</v>
+        <v>720419</v>
       </c>
       <c r="R18" t="n">
-        <v>6368305</v>
+        <v>6368251</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2497,18 +2544,12 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>på fin karstmark</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,60 +2568,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132846311</v>
+        <v>105058146</v>
       </c>
       <c r="B19" t="n">
-        <v>99161</v>
+        <v>102225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>221223</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Gasmyr 900 m NO, under kraftledningen., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720419</v>
+        <v>720491</v>
       </c>
       <c r="R19" t="n">
-        <v>6368251</v>
+        <v>6368273</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2604,12 +2642,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2002-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2002-07-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,29 +2656,37 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkområde under kraftledning.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132846310</v>
+        <v>131912093</v>
       </c>
       <c r="B20" t="n">
-        <v>99795</v>
+        <v>107598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,41 +2694,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde 1:33., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720419</v>
+        <v>720418</v>
       </c>
       <c r="R20" t="n">
-        <v>6368251</v>
+        <v>6368336</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,12 +2748,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,64 +2762,61 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkhällmark.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132846297</v>
+        <v>132846296</v>
       </c>
       <c r="B21" t="n">
-        <v>91340</v>
+        <v>107598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4191</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2825,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på fin karstmark, i fylld karstspricka</t>
+          <t>på fin karstmark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,6 +2889,419 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132846304</v>
+      </c>
+      <c r="B22" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132846299</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132846310</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131912092</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100248</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720388</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6368351</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1946,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132846309</v>
+        <v>134590050</v>
       </c>
       <c r="B13" t="n">
-        <v>5497</v>
+        <v>43472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,37 +1957,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Rävstuhällar, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720419</v>
+        <v>720350</v>
       </c>
       <c r="R13" t="n">
-        <v>6368251</v>
+        <v>6368430</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,12 +2011,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,65 +2041,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132846303</v>
+        <v>134591127</v>
       </c>
       <c r="B14" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Rävstuhällar, Rävstuhällar, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720452</v>
+        <v>720647</v>
       </c>
       <c r="R14" t="n">
-        <v>6368310</v>
+        <v>6368200</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2116,12 +2118,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,79 +2142,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132846311</v>
+        <v>134599714</v>
       </c>
       <c r="B15" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720419</v>
+        <v>720308</v>
       </c>
       <c r="R15" t="n">
-        <v>6368251</v>
+        <v>6368457</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,12 +2234,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,72 +2265,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132846312</v>
+        <v>134599715</v>
       </c>
       <c r="B16" t="n">
-        <v>99230</v>
+        <v>43472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720419</v>
+        <v>720383</v>
       </c>
       <c r="R16" t="n">
-        <v>6368251</v>
+        <v>6368321</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,12 +2351,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,60 +2382,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131912097</v>
+        <v>134599717</v>
       </c>
       <c r="B17" t="n">
-        <v>106324</v>
+        <v>43472</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720408</v>
+        <v>720379</v>
       </c>
       <c r="R17" t="n">
-        <v>6368255</v>
+        <v>6368304</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,12 +2468,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,71 +2492,76 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132846307</v>
+        <v>134599718</v>
       </c>
       <c r="B18" t="n">
-        <v>106324</v>
+        <v>43472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720419</v>
+        <v>720387</v>
       </c>
       <c r="R18" t="n">
-        <v>6368251</v>
+        <v>6368287</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2536,12 +2585,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,28 +2609,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105058146</v>
+        <v>134599719</v>
       </c>
       <c r="B19" t="n">
-        <v>102225</v>
+        <v>43472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,46 +2639,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221223</v>
+        <v>101242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gasmyr 900 m NO, under kraftledningen., Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720491</v>
+        <v>720395</v>
       </c>
       <c r="R19" t="n">
-        <v>6368273</v>
+        <v>6368270</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,12 +2702,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2002-07-19</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2002-07-19</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,37 +2726,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkområde under kraftledning.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131912093</v>
+        <v>134599721</v>
       </c>
       <c r="B20" t="n">
-        <v>107598</v>
+        <v>43472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,34 +2756,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R20" t="n">
-        <v>6368336</v>
+        <v>6368256</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2748,12 +2819,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,33 +2843,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkhällmark.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132846296</v>
+        <v>134599722</v>
       </c>
       <c r="B21" t="n">
-        <v>107598</v>
+        <v>43472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,41 +2873,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720471</v>
+        <v>720400</v>
       </c>
       <c r="R21" t="n">
-        <v>6368305</v>
+        <v>6368231</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2854,17 +2936,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på fin karstmark</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132846304</v>
+        <v>134599726</v>
       </c>
       <c r="B22" t="n">
-        <v>107598</v>
+        <v>43472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,41 +2990,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720452</v>
+        <v>720596</v>
       </c>
       <c r="R22" t="n">
-        <v>6368310</v>
+        <v>6368392</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2961,12 +3053,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,22 +3084,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132846299</v>
+        <v>134599728</v>
       </c>
       <c r="B23" t="n">
-        <v>99858</v>
+        <v>43472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,41 +3107,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222309</v>
+        <v>101242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720452</v>
+        <v>720416</v>
       </c>
       <c r="R23" t="n">
-        <v>6368310</v>
+        <v>6368254</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3063,12 +3170,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,22 +3201,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132846310</v>
+        <v>134599729</v>
       </c>
       <c r="B24" t="n">
-        <v>99858</v>
+        <v>43472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3107,41 +3224,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222309</v>
+        <v>101242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720419</v>
+        <v>720394</v>
       </c>
       <c r="R24" t="n">
-        <v>6368251</v>
+        <v>6368344</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3165,12 +3287,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,60 +3318,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131912092</v>
+        <v>134599730</v>
       </c>
       <c r="B25" t="n">
-        <v>100248</v>
+        <v>43472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222662</v>
+        <v>101242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ardre Botvalde 1:33., Gtl</t>
+          <t>Ardre Botvalde, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720388</v>
+        <v>720370</v>
       </c>
       <c r="R25" t="n">
-        <v>6368351</v>
+        <v>6368395</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,17 +3404,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Källmyr mot V: 50 m x 30 m.</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,26 +3428,2276 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Källmyr.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134599731</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720370</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6368416</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134603618</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720458</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6368241</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 st</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134603622</v>
+      </c>
+      <c r="B28" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720422</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6368439</v>
+      </c>
+      <c r="S28" t="n">
+        <v>12</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 st</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134606272</v>
+      </c>
+      <c r="B29" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720527</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6368189</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134606273</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720484</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6368159</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134606274</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720532</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6368230</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134606276</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720523</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6368264</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132846309</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132846303</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99224</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132846311</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99224</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132846312</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131912097</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720408</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6368255</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132846307</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>105058146</v>
+      </c>
+      <c r="B39" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gasmyr 900 m NO, under kraftledningen., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720491</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6368273</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2002-07-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2002-07-19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkområde under kraftledning.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131912093</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720418</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6368336</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkhällmark.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132846296</v>
+      </c>
+      <c r="B41" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720471</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6368305</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>på fin karstmark</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132846304</v>
+      </c>
+      <c r="B42" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132846299</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6368310</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132846310</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ardre, Botvalde 1:33 1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6368251</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131912092</v>
+      </c>
+      <c r="B45" t="n">
+        <v>100248</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ardre Botvalde 1:33., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720388</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6368351</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Källmyr mot V: 50 m x 30 m.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134591089</v>
+      </c>
+      <c r="B46" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rävstuhällar, Rävstuhällar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720595</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6368274</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca 50 cm</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10274-2026 artfynd.xlsx
+++ b/artfynd/A 10274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846305</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1493,6 +1528,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058135</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846297</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912056</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,6 +1881,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912057</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590050</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591127</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2274,6 +2344,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599714</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2391,6 +2466,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2508,6 +2588,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599717</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2625,6 +2710,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2742,6 +2832,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599719</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2859,6 +2954,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599721</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2976,6 +3076,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599722</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3093,6 +3198,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599726</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3210,6 +3320,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599728</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3327,6 +3442,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599729</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3444,6 +3564,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599730</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3561,6 +3686,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599731</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3673,6 +3803,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134603618</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3785,6 +3920,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134603622</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3892,6 +4032,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134606272</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3999,6 +4144,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134606273</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4111,6 +4261,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134606274</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4218,6 +4373,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134606276</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4315,6 +4475,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846309</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4421,6 +4586,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846303</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4531,6 +4701,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846311</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4641,6 +4816,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846312</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4743,6 +4923,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912097</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4840,6 +5025,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846307</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4955,6 +5145,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105058146</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5057,6 +5252,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912093</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5164,6 +5364,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846296</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5266,6 +5471,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846304</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5368,6 +5578,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846299</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5470,6 +5685,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846310</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5577,6 +5797,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912092</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5698,8 +5923,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>